--- a/ig/nr-add-def-ins-collection/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/ig/nr-add-def-ins-collection/StructureDefinition-fr-core-patient-ins.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-23T11:38:46+00:00</t>
+    <t>2023-11-06T10:27:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil FrPatient appliqué à l'INS.</t>
+    <t>Profil FrPatient appliqué à l'INS avec identité validée.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -11220,7 +11220,7 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>37</v>

--- a/ig/nr-add-def-ins-collection/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/ig/nr-add-def-ins-collection/StructureDefinition-fr-core-patient-ins.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-06T10:27:25+00:00</t>
+    <t>2023-11-06T10:34:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-def-ins-collection/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/ig/nr-add-def-ins-collection/StructureDefinition-fr-core-patient-ins.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-06T10:34:42+00:00</t>
+    <t>2023-11-06T13:10:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil FrPatient appliqué à l'INS avec identité validée.</t>
+    <t>Profil FrPatient appliqué à l'INS avec identité validée. Pour plus d'informations, consulter le référentiel national d'identitovigilance de l'ANS (RNIV).</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/ig/nr-add-def-ins-collection/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/ig/nr-add-def-ins-collection/StructureDefinition-fr-core-patient-ins.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-06T13:10:33+00:00</t>
+    <t>2023-11-06T13:11:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil FrPatient appliqué à l'INS avec identité validée. Pour plus d'informations, consulter le référentiel national d'identitovigilance de l'ANS (RNIV).</t>
+    <t>Profil FrPatient appliqué à l'INS avec identité validée. Pour plus d'informations sur le contexte du patient INS, consultez le référentiel national d'identitovigilance (RNIV) et la documentation du référentiel INS de l'ANS .</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/ig/nr-add-def-ins-collection/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/ig/nr-add-def-ins-collection/StructureDefinition-fr-core-patient-ins.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-06T13:11:32+00:00</t>
+    <t>2023-11-06T13:13:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-def-ins-collection/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/ig/nr-add-def-ins-collection/StructureDefinition-fr-core-patient-ins.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-06T13:13:14+00:00</t>
+    <t>2023-11-06T13:13:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
